--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="119" activeTab="126"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="122" activeTab="129"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -134,6 +134,9 @@
     <sheet name="20251120" sheetId="136" r:id="rId125"/>
     <sheet name="20251121" sheetId="137" r:id="rId126"/>
     <sheet name="20251122" sheetId="138" r:id="rId127"/>
+    <sheet name="20251123" sheetId="139" r:id="rId128"/>
+    <sheet name="20251124" sheetId="140" r:id="rId129"/>
+    <sheet name="20251125" sheetId="141" r:id="rId130"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -235,6 +238,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="124">'20251120'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="125">'20251121'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="126">'20251122'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="127">'20251123'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="128">'20251124'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="129">'20251125'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -276,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="415">
   <si>
     <t>今天计划
 做什么
@@ -2291,6 +2297,49 @@
   <si>
     <t>计组计算
 5题</t>
+  </si>
+  <si>
+    <t>数学
+向量卷</t>
+  </si>
+  <si>
+    <t>数学
+特征值卷</t>
+  </si>
+  <si>
+    <t>网络计算
+5题</t>
+  </si>
+  <si>
+    <t>肖秀荣
+时政</t>
+  </si>
+  <si>
+    <t>系统计算
+5题</t>
+  </si>
+  <si>
+    <t>数学
+二次型</t>
+  </si>
+  <si>
+    <t>数学
+导数和微分</t>
+  </si>
+  <si>
+    <t>数学
+中值定理</t>
+  </si>
+  <si>
+    <t>笔记复习
+至少10个</t>
+  </si>
+  <si>
+    <t>笔记复习
+至少10分</t>
+  </si>
+  <si>
+    <t>KMP算法</t>
   </si>
 </sst>
 </file>
@@ -11685,10 +11734,18 @@
       <c r="A5" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="9" t="s">
         <v>10</v>
@@ -11697,23 +11754,23 @@
     <row r="6" customFormat="1" ht="15.15" spans="1:7">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="7">
         <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="3"/>
@@ -11725,33 +11782,43 @@
       <c r="A7" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>408</v>
+      </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" customFormat="1" ht="15.15" spans="1:7">
       <c r="A8" s="6">
         <f>SUM(B8:F8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" s="7">
         <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="4"/>
@@ -11796,20 +11863,554 @@
       </c>
       <c r="B10" s="13">
         <f>SUM(A8,A6,A4,A2)</f>
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="13">
-        <v>25.83</v>
+        <v>34.5</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="13">
         <f>B10+D10</f>
-        <v>27.08</v>
+        <v>37.75</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251122</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251123</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学
+向量卷</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学
+特征值卷</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>网络计算
+5题</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>系统计算
+5题</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>35.61</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>39.36</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251123</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251124</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学
+二次型</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学
+导数和微分</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>网络计算
+5题</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>计组计算
+5题</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>23.92</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>27.67</v>
       </c>
       <c r="G10" s="14"/>
     </row>
@@ -12092,6 +12693,273 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251124</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251125</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学
+中值定理</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记复习
+至少10个</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>计组计算
+5题</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>系统计算
+5题</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>8.67</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>12.42</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="122" activeTab="129"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="124" activeTab="131"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -137,6 +137,8 @@
     <sheet name="20251123" sheetId="139" r:id="rId128"/>
     <sheet name="20251124" sheetId="140" r:id="rId129"/>
     <sheet name="20251125" sheetId="141" r:id="rId130"/>
+    <sheet name="20251126" sheetId="142" r:id="rId131"/>
+    <sheet name="20251127" sheetId="143" r:id="rId132"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -241,6 +243,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="127">'20251123'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="128">'20251124'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="129">'20251125'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="130">'20251126'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="131">'20251127'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -282,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="416">
   <si>
     <t>今天计划
 做什么
@@ -2340,6 +2344,10 @@
   </si>
   <si>
     <t>KMP算法</t>
+  </si>
+  <si>
+    <t>660视频
+10集</t>
   </si>
 </sst>
 </file>
@@ -12964,6 +12972,519 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet131.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251125</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251126</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>KMP算法</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记复习
+至少10分</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记复习
+至少10分</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>22.43</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>26.18</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet132.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251126</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251127</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>0</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+10集</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+10集</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>22.43</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>23.68</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="124" activeTab="131"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="126" activeTab="133"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -139,6 +139,8 @@
     <sheet name="20251125" sheetId="141" r:id="rId130"/>
     <sheet name="20251126" sheetId="142" r:id="rId131"/>
     <sheet name="20251127" sheetId="143" r:id="rId132"/>
+    <sheet name="20251128" sheetId="144" r:id="rId133"/>
+    <sheet name="20251129" sheetId="145" r:id="rId134"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -245,6 +247,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="129">'20251125'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="130">'20251126'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="131">'20251127'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="132">'20251128'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="133">'20251129'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -286,7 +290,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="427">
   <si>
     <t>今天计划
 做什么
@@ -2348,6 +2352,61 @@
   <si>
     <t>660视频
 10集</t>
+  </si>
+  <si>
+    <t>肖秀荣
+时政
+国外</t>
+  </si>
+  <si>
+    <t>肖秀荣
+时政
+国内</t>
+  </si>
+  <si>
+    <t>660视频
+20集</t>
+  </si>
+  <si>
+    <t>Prim
+Kruskal
+Floyd</t>
+  </si>
+  <si>
+    <t>进程前趋图
+死锁检测</t>
+  </si>
+  <si>
+    <t>并查集
+线索二叉树</t>
+  </si>
+  <si>
+    <t>肖秀荣
+时政
+国外
+*2</t>
+  </si>
+  <si>
+    <t>数据结构
+计算题
+生成器
+1-4</t>
+  </si>
+  <si>
+    <t>数据结构
+计算题
+生成器
+5-8</t>
+  </si>
+  <si>
+    <t>数据结构
+计算题
+生成器
+9-12</t>
+  </si>
+  <si>
+    <t>肖八
+*2</t>
   </si>
 </sst>
 </file>
@@ -13137,13 +13196,13 @@
         <v>415</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G7" s="10"/>
     </row>
@@ -13261,13 +13320,13 @@
         <v>415</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
@@ -13307,6 +13366,8 @@
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
       <c r="F3" s="5"/>
       <c r="G3" s="4" t="s">
         <v>57</v>
@@ -13346,11 +13407,21 @@
       <c r="A5" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>10</v>
       </c>
@@ -13358,27 +13429,559 @@
     <row r="6" customFormat="1" ht="15.15" spans="1:7">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="B6" s="7">
         <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+10集</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+10集</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政
+国外</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政
+国内</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政
+国内</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>26.18</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>29.93</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet133.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251127</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251128</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+20集</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>Prim
+Kruskal
+Floyd</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>进程前趋图
+死锁检测</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>并查集
+线索二叉树</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖秀荣
+时政
+国外
+*2</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>48.95</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>52.7</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet134.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251128</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251129</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -13427,27 +14030,33 @@
       <c r="B9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
         <v>660视频
-10集</v>
+20集</v>
       </c>
       <c r="C9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>660视频
-10集</v>
+        <v>数据结构
+计算题
+生成器
+1-4</v>
       </c>
       <c r="D9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>肖秀荣
-时政</v>
+        <v>数据结构
+计算题
+生成器
+5-8</v>
       </c>
       <c r="E9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>肖秀荣
-时政</v>
+        <v>数据结构
+计算题
+生成器
+9-12</v>
       </c>
       <c r="F9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>肖秀荣
-时政</v>
+        <v>肖八
+*2</v>
       </c>
       <c r="G9" s="10"/>
     </row>
@@ -13457,20 +14066,20 @@
       </c>
       <c r="B10" s="13">
         <f>SUM(A8,A6,A4,A2)</f>
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="13">
-        <v>22.43</v>
+        <v>0</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="13">
         <f>B10+D10</f>
-        <v>23.68</v>
+        <v>1.5</v>
       </c>
       <c r="G10" s="14"/>
     </row>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="126" activeTab="133"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="133" activeTab="136"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -141,6 +141,9 @@
     <sheet name="20251127" sheetId="143" r:id="rId132"/>
     <sheet name="20251128" sheetId="144" r:id="rId133"/>
     <sheet name="20251129" sheetId="145" r:id="rId134"/>
+    <sheet name="20251130" sheetId="146" r:id="rId135"/>
+    <sheet name="20251201" sheetId="147" r:id="rId136"/>
+    <sheet name="20251202" sheetId="149" r:id="rId137"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -249,6 +252,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="131">'20251127'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="132">'20251128'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="133">'20251129'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="134">'20251130'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="135">'20251201'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="136">'20251202'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -290,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2911" uniqueCount="439">
   <si>
     <t>今天计划
 做什么
@@ -2407,6 +2413,68 @@
   <si>
     <t>肖八
 *2</t>
+  </si>
+  <si>
+    <t>660视频
+18集</t>
+  </si>
+  <si>
+    <t>数学刷题器
+线代基本</t>
+  </si>
+  <si>
+    <t>肖八</t>
+  </si>
+  <si>
+    <t>笔记保温
+*40</t>
+  </si>
+  <si>
+    <t>系统计算
+*10
+数据计算
+*10
+计组计算
+*10
+网络计算
+*10</t>
+  </si>
+  <si>
+    <t>数学刷题器
+常线微分</t>
+  </si>
+  <si>
+    <t>数学刷题器
+线代常用</t>
+  </si>
+  <si>
+    <t>政治大题
+解题方法</t>
+  </si>
+  <si>
+    <t>系统计算
+*10
+数据计算
+*9</t>
+  </si>
+  <si>
+    <t>政治大题
+12套
+2套</t>
+  </si>
+  <si>
+    <t>线代基本
+*10
+线代常用
+*10
+微分方程
+*10</t>
+  </si>
+  <si>
+    <t>系统计算
+*10
+数据计算
+*10</t>
   </si>
 </sst>
 </file>
@@ -13947,10 +14015,18 @@
       <c r="A5" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F5" s="5" t="s">
         <v>9</v>
       </c>
@@ -13961,27 +14037,824 @@
     <row r="6" customFormat="1" ht="15.15" spans="1:7">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="B6" s="7">
         <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="3"/>
         <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+20集</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数据结构
+计算题
+生成器
+1-4</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数据结构
+计算题
+生成器
+5-8</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数据结构
+计算题
+生成器
+9-12</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖八
+*2</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>22.98</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>26.73</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet135.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251129</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251130</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+20集</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+20集</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>660视频
+18集</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学刷题器
+线代基本</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖八</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>4.17</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>7.92</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet136.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251130</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251201</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*40</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>系统计算
+*10
+数据计算
+*10
+计组计算
+*10
+网络计算
+*10</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学刷题器
+常线微分</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学刷题器
+线代常用</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>政治大题
+解题方法</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.25</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>18.9</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>22.15</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet137.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251201</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251202</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -14029,34 +14902,41 @@
       </c>
       <c r="B9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>660视频
-20集</v>
+        <v>笔记保温
+*40</v>
       </c>
       <c r="C9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>数据结构
-计算题
-生成器
-1-4</v>
+        <v>系统计算
+*10
+数据计算
+*9</v>
       </c>
       <c r="D9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>数据结构
-计算题
-生成器
-5-8</v>
+        <v>政治大题
+12套
+2套</v>
       </c>
       <c r="E9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>数据结构
-计算题
-生成器
-9-12</v>
+        <v>线代基本
+*10
+线代常用
+*10
+微分方程
+*10</v>
       </c>
       <c r="F9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>肖八
-*2</v>
+        <v>系统计算
+*10
+数据计算
+*10
+计组计算
+*10
+网络计算
+*10</v>
       </c>
       <c r="G9" s="10"/>
     </row>
@@ -14066,7 +14946,7 @@
       </c>
       <c r="B10" s="13">
         <f>SUM(A8,A6,A4,A2)</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>17</v>
@@ -14079,7 +14959,7 @@
       </c>
       <c r="F10" s="13">
         <f>B10+D10</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G10" s="14"/>
     </row>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="133" activeTab="136"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="135" activeTab="137"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -144,6 +144,7 @@
     <sheet name="20251130" sheetId="146" r:id="rId135"/>
     <sheet name="20251201" sheetId="147" r:id="rId136"/>
     <sheet name="20251202" sheetId="149" r:id="rId137"/>
+    <sheet name="20251203" sheetId="150" r:id="rId138"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -255,6 +256,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="134">'20251130'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="135">'20251201'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="136">'20251202'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="137">'20251203'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -296,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2911" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="449">
   <si>
     <t>今天计划
 做什么
@@ -2458,9 +2460,9 @@
 *9</t>
   </si>
   <si>
-    <t>政治大题
-12套
-2套</t>
+    <t>政治
+大题总结
+10题</t>
   </si>
   <si>
     <t>线代基本
@@ -2471,10 +2473,75 @@
 *10</t>
   </si>
   <si>
-    <t>系统计算
-*10
-数据计算
-*10</t>
+    <t>二叉树
+的公式
+h
+~
+(2^h)-1
+以及
+n0=n2+1</t>
+  </si>
+  <si>
+    <t>KMP算法
+next[i]
+看0~i-1
+子串的
+最长相同前后缀
+长度</t>
+  </si>
+  <si>
+    <t>中共抗日
+四大作用
+率先抗日
+统一战线
+建立
+根据地
+正确方向
+(持久战)</t>
+  </si>
+  <si>
+    <t>ack_seq
+指期望
+下次收到
+第一个
+字节序</t>
+  </si>
+  <si>
+    <t>ip数据报
+数据部分
+按8字节
+为单位
+分片
+最后分片
+无需8倍</t>
+  </si>
+  <si>
+    <t>笔记保温
+*34</t>
+  </si>
+  <si>
+    <t>政治
+大题总结
+5题</t>
+  </si>
+  <si>
+    <t>二进制
+指数退避
+(2^k)-1
+k=
+min(r,10)</t>
+  </si>
+  <si>
+    <t>笔记保温
+*20</t>
+  </si>
+  <si>
+    <t>专业计算
+10</t>
+  </si>
+  <si>
+    <t>数学计算
+10</t>
   </si>
 </sst>
 </file>
@@ -14612,10 +14679,10 @@
         <v>436</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>437</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="G7" s="10"/>
     </row>
@@ -14737,16 +14804,16 @@
         <v>430</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>436</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>437</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
@@ -14786,7 +14853,21 @@
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="B3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>442</v>
+      </c>
       <c r="G3" s="4" t="s">
         <v>57</v>
       </c>
@@ -14794,27 +14875,27 @@
     <row r="4" customFormat="1" ht="15.15" spans="1:7">
       <c r="A4" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="B4" s="7">
         <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C4" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E4" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F4" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="8" t="str" cm="1">
         <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
@@ -14825,7 +14906,15 @@
       <c r="A5" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="9" t="s">
         <v>10</v>
@@ -14834,11 +14923,11 @@
     <row r="6" customFormat="1" ht="15.15" spans="1:7">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="B6" s="7">
         <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="7">
         <f t="shared" si="3"/>
@@ -14846,11 +14935,11 @@
       </c>
       <c r="D6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="3"/>
@@ -14862,21 +14951,31 @@
       <c r="A7" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>437</v>
+      </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" customFormat="1" ht="15.15" spans="1:7">
       <c r="A8" s="6">
         <f>SUM(B8:F8)</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="B8" s="7">
         <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C8" s="7">
         <f t="shared" si="4"/>
@@ -14884,11 +14983,11 @@
       </c>
       <c r="D8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="4"/>
@@ -14914,12 +15013,18 @@
       </c>
       <c r="D9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
-        <v>政治大题
-12套
-2套</v>
+        <v>政治
+大题总结
+10题</v>
       </c>
       <c r="E9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>政治
+大题总结
+10题</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
         <v>线代基本
 *10
 线代常用
@@ -14927,15 +15032,285 @@
 微分方程
 *10</v>
       </c>
-      <c r="F9" s="11" t="str" cm="1">
-        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>5.25</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>126.88</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>132.13</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251202</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251203</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*34</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
         <v>系统计算
 *10
 数据计算
+*9</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>政治
+大题总结
+10题</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>政治
+大题总结
+5题</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>线代基本
 *10
-计组计算
+线代常用
 *10
-网络计算
+微分方程
 *10</v>
       </c>
       <c r="G9" s="10"/>
@@ -14946,20 +15321,20 @@
       </c>
       <c r="B10" s="13">
         <f>SUM(A8,A6,A4,A2)</f>
-        <v>1.25</v>
+        <v>4.25</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="13">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="13">
         <f>B10+D10</f>
-        <v>1.25</v>
+        <v>34.85</v>
       </c>
       <c r="G10" s="14"/>
     </row>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="135" activeTab="137"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="137" activeTab="140"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -145,6 +145,9 @@
     <sheet name="20251201" sheetId="147" r:id="rId136"/>
     <sheet name="20251202" sheetId="149" r:id="rId137"/>
     <sheet name="20251203" sheetId="150" r:id="rId138"/>
+    <sheet name="20251204" sheetId="151" r:id="rId139"/>
+    <sheet name="20251205" sheetId="152" r:id="rId140"/>
+    <sheet name="20251206" sheetId="153" r:id="rId141"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -257,6 +260,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="135">'20251201'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="136">'20251202'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="137">'20251203'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="138">'20251204'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="139">'20251205'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="140">'20251206'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -298,7 +304,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3026" uniqueCount="455">
   <si>
     <t>今天计划
 做什么
@@ -2533,7 +2539,7 @@
   </si>
   <si>
     <t>笔记保温
-*20</t>
+*10</t>
   </si>
   <si>
     <t>专业计算
@@ -2542,6 +2548,34 @@
   <si>
     <t>数学计算
 10</t>
+  </si>
+  <si>
+    <t>卷子
+2025
+408</t>
+  </si>
+  <si>
+    <t>卷子
+2022
+数二</t>
+  </si>
+  <si>
+    <t>笔记保温
+*20</t>
+  </si>
+  <si>
+    <t>卷子
+2024
+408</t>
+  </si>
+  <si>
+    <t>卷子
+2023
+数二</t>
+  </si>
+  <si>
+    <t>笔记保温
+*17</t>
   </si>
 </sst>
 </file>
@@ -14750,7 +14784,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" ht="15.15" spans="1:7">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -15239,7 +15273,7 @@
         <v>447</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>444</v>
@@ -15335,6 +15369,275 @@
       <c r="F10" s="13">
         <f>B10+D10</f>
         <v>34.85</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet139.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251203</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251204</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*10</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>专业计算
+10</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*10</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>政治
+大题总结
+5题</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学计算
+10</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>26.13</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>29.88</v>
       </c>
       <c r="G10" s="14"/>
     </row>
@@ -15602,6 +15905,542 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet140.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251204</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251205</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2025
+408</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2025
+408</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2022
+数二</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*20</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2022
+数二</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.25</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>35.03</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>38.28</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet141.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251205</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251206</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>0.75</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2024
+408</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2024
+408</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2023
+数二</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*17</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2022
+数二</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>2.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>38.42</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>41.17</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="137" activeTab="140"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="133" activeTab="141"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -148,6 +148,7 @@
     <sheet name="20251204" sheetId="151" r:id="rId139"/>
     <sheet name="20251205" sheetId="152" r:id="rId140"/>
     <sheet name="20251206" sheetId="153" r:id="rId141"/>
+    <sheet name="20251207" sheetId="154" r:id="rId142"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -263,6 +264,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="138">'20251204'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="139">'20251205'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="140">'20251206'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="141">'20251207'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -304,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3026" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="457">
   <si>
     <t>今天计划
 做什么
@@ -2576,6 +2578,15 @@
   <si>
     <t>笔记保温
 *17</t>
+  </si>
+  <si>
+    <t>笔记保温
+*13</t>
+  </si>
+  <si>
+    <t>卷子
+2023
+408</t>
   </si>
 </sst>
 </file>
@@ -16345,7 +16356,7 @@
         <v>454</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G7" s="10"/>
     </row>
@@ -16431,6 +16442,274 @@
       <c r="F10" s="13">
         <f>B10+D10</f>
         <v>41.17</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet142.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251206</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251207</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*20</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2024
+408</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2023
+数二</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*17</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2023
+数二</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.25</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>36.13</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>39.38</v>
       </c>
       <c r="G10" s="14"/>
     </row>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="133" activeTab="141"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="137" activeTab="145"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -149,6 +149,10 @@
     <sheet name="20251205" sheetId="152" r:id="rId140"/>
     <sheet name="20251206" sheetId="153" r:id="rId141"/>
     <sheet name="20251207" sheetId="154" r:id="rId142"/>
+    <sheet name="20251208" sheetId="155" r:id="rId143"/>
+    <sheet name="20251209" sheetId="156" r:id="rId144"/>
+    <sheet name="20251210" sheetId="157" r:id="rId145"/>
+    <sheet name="20251211" sheetId="158" r:id="rId146"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -265,6 +269,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="139">'20251205'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="140">'20251206'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="141">'20251207'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="142">'20251208'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="143">'20251209'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="144">'20251210'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="145">'20251211'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -306,7 +314,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="473">
   <si>
     <t>今天计划
 做什么
@@ -2587,6 +2595,79 @@
     <t>卷子
 2023
 408</t>
+  </si>
+  <si>
+    <t>肖四
+1</t>
+  </si>
+  <si>
+    <t>卷子
+2017
+数二</t>
+  </si>
+  <si>
+    <t>卷子
+2024
+数二</t>
+  </si>
+  <si>
+    <t>卷子
+2022
+408</t>
+  </si>
+  <si>
+    <t>笔记保温
+*14.5</t>
+  </si>
+  <si>
+    <t>卷子
+2021
+数二</t>
+  </si>
+  <si>
+    <t>肖四
+选择
+2、3、4</t>
+  </si>
+  <si>
+    <t>肖四
+大题
+1</t>
+  </si>
+  <si>
+    <t>肖四
+大题
+2</t>
+  </si>
+  <si>
+    <t>卷子
+2025
+数二</t>
+  </si>
+  <si>
+    <t>笔记浓缩</t>
+  </si>
+  <si>
+    <t>肖四
+选择
+4</t>
+  </si>
+  <si>
+    <t>肖四
+大题
+3</t>
+  </si>
+  <si>
+    <t>一页纸</t>
+  </si>
+  <si>
+    <t>笔记保温
+20</t>
+  </si>
+  <si>
+    <t>肖四
+大题
+4</t>
   </si>
 </sst>
 </file>
@@ -15629,7 +15710,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" ht="15.15" spans="1:7">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -16619,13 +16700,13 @@
         <v>456</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>451</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="G7" s="10"/>
     </row>
@@ -16710,6 +16791,1077 @@
       <c r="F10" s="13">
         <f>B10+D10</f>
         <v>39.38</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet143.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251207</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251208</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>0.75</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*13</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2023
+408</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+1</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*20</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2017
+数二</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>2.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>31.97</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>34.72</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet144.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251208</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251209</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2024
+数二</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2022
+408</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+1</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+*14.5</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2021
+数二</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>35.32</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>39.07</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet145.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251209</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251210</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>0.5</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2024
+数二</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+选择
+2、3、4</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+大题
+1</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+大题
+2</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>卷子
+2025
+数二</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>2.25</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>59.12</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>61.37</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet146.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251210</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251211</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记浓缩</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+选择
+4</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+大题
+1</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+大题
+2</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四
+大题
+3</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>34.8</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>38.55</v>
       </c>
       <c r="G10" s="14"/>
     </row>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="137" activeTab="145"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="146" activeTab="149"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -153,6 +153,10 @@
     <sheet name="20251209" sheetId="156" r:id="rId144"/>
     <sheet name="20251210" sheetId="157" r:id="rId145"/>
     <sheet name="20251211" sheetId="158" r:id="rId146"/>
+    <sheet name="20251212" sheetId="159" r:id="rId147"/>
+    <sheet name="20251213" sheetId="160" r:id="rId148"/>
+    <sheet name="20251214" sheetId="161" r:id="rId149"/>
+    <sheet name="20251215" sheetId="162" r:id="rId150"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -273,6 +277,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="143">'20251209'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="144">'20251210'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="145">'20251211'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="146">'20251212'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="147">'20251213'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="148">'20251214'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="149">'20251215'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -314,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3245" uniqueCount="481">
   <si>
     <t>今天计划
 做什么
@@ -2658,16 +2666,50 @@
 3</t>
   </si>
   <si>
-    <t>一页纸</t>
+    <t>一页纸
+60</t>
+  </si>
+  <si>
+    <t>专业真题
+采集</t>
+  </si>
+  <si>
+    <t>数学真题
+采集</t>
+  </si>
+  <si>
+    <t>肖四大题
+4</t>
+  </si>
+  <si>
+    <t>一页纸
+50</t>
   </si>
   <si>
     <t>笔记保温
-20</t>
-  </si>
-  <si>
-    <t>肖四
-大题
-4</t>
+10</t>
+  </si>
+  <si>
+    <t>笔记保温
+3</t>
+  </si>
+  <si>
+    <t>数二
+2024
+保温</t>
+  </si>
+  <si>
+    <t>数二
+2025
+保温</t>
+  </si>
+  <si>
+    <t>笔记保温
+5</t>
+  </si>
+  <si>
+    <t>笔记保温
+3.1</t>
   </si>
 </sst>
 </file>
@@ -17768,16 +17810,16 @@
         <v>470</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>471</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G7" s="10"/>
     </row>
@@ -17862,6 +17904,807 @@
       <c r="F10" s="13">
         <f>B10+D10</f>
         <v>38.55</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet147.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251211</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251212</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>专业真题
+采集</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数学真题
+采集</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖四大题
+4</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>28.22</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>31.97</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet148.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251212</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251213</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+50</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>42.72</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>46.47</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet149.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251213</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251214</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+10</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+3</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+10</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+10</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>36.17</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>39.92</v>
       </c>
       <c r="G10" s="14"/>
     </row>
@@ -18126,6 +18969,257 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet150.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251214</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251215</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>0</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数二
+2024
+保温</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数二
+2025
+保温</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+5</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+3.1</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>36.17</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>37.67</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/工作报告.xlsx
+++ b/工作报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="146" activeTab="149"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="153" activeTab="156"/>
   </bookViews>
   <sheets>
     <sheet name="20250519" sheetId="1" r:id="rId1"/>
@@ -157,6 +157,13 @@
     <sheet name="20251213" sheetId="160" r:id="rId148"/>
     <sheet name="20251214" sheetId="161" r:id="rId149"/>
     <sheet name="20251215" sheetId="162" r:id="rId150"/>
+    <sheet name="20251216" sheetId="163" r:id="rId151"/>
+    <sheet name="20251217" sheetId="164" r:id="rId152"/>
+    <sheet name="20251218" sheetId="165" r:id="rId153"/>
+    <sheet name="20251219" sheetId="166" r:id="rId154"/>
+    <sheet name="20251220" sheetId="167" r:id="rId155"/>
+    <sheet name="20251221" sheetId="168" r:id="rId156"/>
+    <sheet name="20251222" sheetId="169" r:id="rId157"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'20250620'!$A$1:$G$10</definedName>
@@ -281,6 +288,13 @@
     <definedName name="_xlnm.Print_Area" localSheetId="147">'20251213'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="148">'20251214'!$A$1:$G$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="149">'20251215'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="150">'20251216'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="151">'20251217'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="152">'20251218'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="153">'20251219'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="154">'20251220'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="155">'20251221'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="156">'20251222'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -322,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3245" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3435" uniqueCount="508">
   <si>
     <t>今天计划
 做什么
@@ -2699,17 +2713,154 @@
 保温</t>
   </si>
   <si>
+    <t>笔记保温
+5</t>
+  </si>
+  <si>
+    <t>笔记保温
+3.1</t>
+  </si>
+  <si>
+    <t>一页纸
+49</t>
+  </si>
+  <si>
     <t>数二
 2025
 保温</t>
   </si>
   <si>
     <t>笔记保温
-5</t>
+60</t>
+  </si>
+  <si>
+    <t>一页纸
+109</t>
+  </si>
+  <si>
+    <t>英语二
+2024</t>
+  </si>
+  <si>
+    <t>数二
+2025
+保温
+填空大题</t>
+  </si>
+  <si>
+    <t>肖4肖8
+60</t>
   </si>
   <si>
     <t>笔记保温
-3.1</t>
+120</t>
+  </si>
+  <si>
+    <t>一页纸
+120</t>
+  </si>
+  <si>
+    <t>计算题
+专业
++
+数学
+20</t>
+  </si>
+  <si>
+    <t>大牙
+抄材料</t>
+  </si>
+  <si>
+    <t>肖4肖8
+54.5</t>
+  </si>
+  <si>
+    <t>计算题
+专业
++
+数学
+16</t>
+  </si>
+  <si>
+    <t>墨墨
+专业
++
+数学
+240</t>
+  </si>
+  <si>
+    <t>新思想
+概念蓝图
+训练
+40</t>
+  </si>
+  <si>
+    <t>模拟卷
+视频
+*10</t>
+  </si>
+  <si>
+    <t>肖4肖8
+45</t>
+  </si>
+  <si>
+    <t>大题
+答题方向
+训练
+20</t>
+  </si>
+  <si>
+    <t>新思想
+概念蓝图
+训练
+29</t>
+  </si>
+  <si>
+    <t>肖4肖8
+58.5</t>
+  </si>
+  <si>
+    <t>大题
+答题方向
+训练
+19</t>
+  </si>
+  <si>
+    <t>新思想
+概念蓝图
+训练
+36</t>
+  </si>
+  <si>
+    <t>肖4肖8
+56.5</t>
+  </si>
+  <si>
+    <t>墨墨
+专业
++
+数学
+120</t>
+  </si>
+  <si>
+    <t>计算题
+数学
++
+专业
+20</t>
+  </si>
+  <si>
+    <t>小程序
+王道
+习题集
+*20</t>
+  </si>
+  <si>
+    <t>速查手册
+扫盲</t>
+  </si>
+  <si>
+    <t>学习x86</t>
   </si>
 </sst>
 </file>
@@ -18614,16 +18765,16 @@
         <v>470</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>480</v>
       </c>
       <c r="G7" s="10"/>
     </row>
@@ -18993,16 +19144,16 @@
         <v>470</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>480</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
@@ -19081,13 +19232,21 @@
       <c r="A5" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>10</v>
       </c>
@@ -19095,19 +19254,19 @@
     <row r="6" customFormat="1" ht="15.15" spans="1:7">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="B6" s="7">
         <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" si="3"/>
@@ -19115,7 +19274,7 @@
       </c>
       <c r="F6" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -19123,37 +19282,47 @@
       <c r="A7" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>482</v>
+      </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" customFormat="1" ht="15.15" spans="1:7">
       <c r="A8" s="6">
         <f>SUM(B8:F8)</f>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="B8" s="7">
         <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="10"/>
     </row>
@@ -19168,9 +19337,276 @@
       </c>
       <c r="C9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
         <v>数二
 2024
 保温</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+5</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+3.1</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>48.1</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>51.85</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet151.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251215</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251216</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+60</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+49</v>
       </c>
       <c r="D9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
@@ -19181,12 +19617,12 @@
       <c r="E9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
         <v>笔记保温
-5</v>
+60</v>
       </c>
       <c r="F9" s="11" t="str" cm="1">
         <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
         <v>笔记保温
-3.1</v>
+60</v>
       </c>
       <c r="G9" s="10"/>
     </row>
@@ -19196,20 +19632,1663 @@
       </c>
       <c r="B10" s="13">
         <f>SUM(A8,A6,A4,A2)</f>
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="13">
-        <v>36.17</v>
+        <v>45.5</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="13">
         <f>B10+D10</f>
-        <v>37.67</v>
+        <v>49.25</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet152.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251216</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251217</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:7">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+109</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>英语二
+2024</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>数二
+2025
+保温
+填空大题</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖4肖8
+60</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+120</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>41.6</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>45.35</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet153.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251217</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251218</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>一页纸
+120</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>计算题
+专业
++
+数学
+20</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>大牙
+抄材料</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖4肖8
+54.5</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>笔记保温
+120</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:9">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>41.05</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>44.8</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet154.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251218</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251219</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>墨墨
+专业
++
+数学
+240</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>新思想
+概念蓝图
+训练
+40</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>模拟卷
+视频
+*10</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖4肖8
+45</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>大题
+答题方向
+训练
+20</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:9">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>36.88</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>40.63</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet155.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251219</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251220</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>墨墨
+专业
++
+数学
+240</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>新思想
+概念蓝图
+训练
+29</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>模拟卷
+视频
+*10</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖4肖8
+58.5</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>大题
+答题方向
+训练
+19</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:9">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>3.75</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet156.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251220</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251221</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>墨墨
+专业
++
+数学
+240</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>新思想
+概念蓝图
+训练
+36</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>模拟卷
+视频
+*10</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>肖4肖8
+56.5</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>大题
+答题方向
+训练
+19</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:9">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.75</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>3.75</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G5:G10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet157.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="6" width="10.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.7777777777778" customWidth="1"/>
+    <col min="8" max="16384" width="15.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A6" si="0">SUM(B2:F2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="B2" s="7">
+        <f t="shared" ref="B2:F2" si="1">IF(COUNTA(B1)&gt;0,0.25,0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f ca="1">INDEX(_wpsfn.SHEETSNAME(),MAX(1,MATCH(G4,_wpsfn.SHEETSNAME(),0)-1))</f>
+        <v>20251221</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:F4" si="2">IF(COUNTA(B3)&gt;0,IF(COUNTA(B1),0.5,0.25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="str" cm="1">
+        <f ca="1" t="array" ref="G4">_wpsfn.SHEETSNAME(A1)</f>
+        <v>20251222</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <f t="shared" ref="B6:F6" si="3">IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" customFormat="1" ht="15.15" spans="1:9">
+      <c r="A8" s="6">
+        <f>SUM(B8:F8)</f>
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <f t="shared" ref="B8:F8" si="4">IF(COUNTA(B7)&gt;0,IF(COUNTA(B1)&gt;0,IF(B5="完成",0.25,0),IF(B5="遗忘",0,0.25)),0)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="125" customHeight="1" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="B9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>墨墨
+专业
++
+数学
+120</v>
+      </c>
+      <c r="C9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="C9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>计算题
+数学
++
+专业
+20</v>
+      </c>
+      <c r="D9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="D9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>模拟卷
+视频
+*10</v>
+      </c>
+      <c r="E9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="E9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>小程序
+王道
+习题集
+*20</v>
+      </c>
+      <c r="F9" s="11" t="str" cm="1">
+        <f ca="1" t="array" ref="F9">IF(COUNTA(INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)))&gt;0,INDIRECT(_xlfn.CONCAT($G2,"!",CHAR(64+COLUMN()),7)),"")</f>
+        <v>速查手册
+扫盲</v>
+      </c>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="15.15" spans="1:9">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13">
+        <f>SUM(A8,A6,A4,A2)</f>
+        <v>3.25</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13">
+        <f>B10+D10</f>
+        <v>3.25</v>
       </c>
       <c r="G10" s="14"/>
     </row>
